--- a/db/mmFB.xlsx
+++ b/db/mmFB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/celltypeAnno/public_version/v0.2/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078EFE4A-62F0-4B4A-9495-B8D9417FE649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3607C42F-0C19-F045-8B33-D028D525DEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="5340" windowWidth="27820" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="5100" windowWidth="25880" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="758">
   <si>
     <t>tissueType</t>
   </si>
@@ -1703,9 +1703,6 @@
     <t>Glut_F14</t>
   </si>
   <si>
-    <t>Glut_F15</t>
-  </si>
-  <si>
     <t>Glut_F16</t>
   </si>
   <si>
@@ -1730,12 +1727,6 @@
     <t>Glut_F24</t>
   </si>
   <si>
-    <t>Glut_F25</t>
-  </si>
-  <si>
-    <t>Glut_F26</t>
-  </si>
-  <si>
     <t>Glut_F27</t>
   </si>
   <si>
@@ -1751,9 +1742,6 @@
     <t>Glut_F39</t>
   </si>
   <si>
-    <t>Glut_F40</t>
-  </si>
-  <si>
     <t>Glut_F41</t>
   </si>
   <si>
@@ -2294,7 +2282,31 @@
     <t>Glutamatergic neurons (mixed)</t>
   </si>
   <si>
-    <t>Glut_F39a</t>
+    <t>Forebrain glutamatergic -&gt; GABA</t>
+  </si>
+  <si>
+    <t>Forebrain glutamatergic/GABA ?</t>
+  </si>
+  <si>
+    <t>Forebrain GABA -&gt; Glut</t>
+  </si>
+  <si>
+    <t>Glut_F26 (mixed)</t>
+  </si>
+  <si>
+    <t>Forebrain glutamatergic-&gt;GABA</t>
+  </si>
+  <si>
+    <t>Glut_F39c</t>
+  </si>
+  <si>
+    <t>GABA_F25c</t>
+  </si>
+  <si>
+    <t>GABA_F40c</t>
+  </si>
+  <si>
+    <t>GABA_F15c</t>
   </si>
 </sst>
 </file>
@@ -2680,7 +2692,7 @@
     <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2725,10 +2737,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E2" t="s">
         <v>200</v>
@@ -2737,10 +2749,10 @@
         <v>200</v>
       </c>
       <c r="I2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2748,10 +2760,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C3" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -2763,10 +2775,10 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
+        <v>615</v>
+      </c>
+      <c r="K3" t="s">
         <v>619</v>
-      </c>
-      <c r="K3" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2774,10 +2786,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C4" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
@@ -2786,13 +2798,13 @@
         <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="I4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2800,10 +2812,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C5" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E5" t="s">
         <v>198</v>
@@ -2812,13 +2824,13 @@
         <v>198</v>
       </c>
       <c r="G5" t="s">
+        <v>622</v>
+      </c>
+      <c r="I5" t="s">
+        <v>615</v>
+      </c>
+      <c r="K5" t="s">
         <v>626</v>
-      </c>
-      <c r="I5" t="s">
-        <v>619</v>
-      </c>
-      <c r="K5" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2826,25 +2838,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C6" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E6" t="s">
         <v>163</v>
       </c>
       <c r="F6" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="G6" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="I6" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -2852,25 +2864,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C7" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E7" t="s">
+        <v>632</v>
+      </c>
+      <c r="F7" t="s">
+        <v>632</v>
+      </c>
+      <c r="G7" t="s">
         <v>636</v>
       </c>
-      <c r="F7" t="s">
-        <v>636</v>
-      </c>
-      <c r="G7" t="s">
-        <v>640</v>
-      </c>
       <c r="I7" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K7" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2878,25 +2890,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C8" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="E8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="G8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="I8" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K8" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2904,25 +2916,25 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" t="s">
+        <v>640</v>
+      </c>
+      <c r="G9" t="s">
+        <v>641</v>
+      </c>
+      <c r="I9" t="s">
+        <v>615</v>
+      </c>
+      <c r="K9" t="s">
         <v>642</v>
-      </c>
-      <c r="C9" t="s">
-        <v>643</v>
-      </c>
-      <c r="E9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G9" t="s">
-        <v>645</v>
-      </c>
-      <c r="I9" t="s">
-        <v>619</v>
-      </c>
-      <c r="K9" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2930,25 +2942,25 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C10" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E10" t="s">
         <v>196</v>
       </c>
       <c r="F10" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G10" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I10" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -2956,25 +2968,25 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C11" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E11" t="s">
         <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="G11" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I11" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K11" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -2982,25 +2994,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="E12" t="s">
         <v>196</v>
       </c>
       <c r="F12" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G12" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I12" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K12" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -3008,25 +3020,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C13" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E13" t="s">
         <v>196</v>
       </c>
       <c r="F13" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="G13" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I13" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -3034,25 +3046,25 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C14" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E14" t="s">
         <v>196</v>
       </c>
       <c r="F14" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="G14" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I14" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K14" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -3060,25 +3072,25 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C15" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E15" t="s">
         <v>196</v>
       </c>
       <c r="F15" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G15" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I15" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K15" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -3086,25 +3098,25 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C16" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E16" t="s">
         <v>196</v>
       </c>
       <c r="F16" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G16" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I16" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K16" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -3112,28 +3124,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C17" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E17" t="s">
         <v>196</v>
       </c>
       <c r="F17" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="G17" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="H17" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="I17" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -3141,22 +3153,22 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E18" t="s">
         <v>202</v>
       </c>
       <c r="F18" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="I18" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -3164,22 +3176,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C19" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E19" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F19" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="I19" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K19" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -3187,22 +3199,22 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C20" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E20" t="s">
         <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="I20" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -3210,10 +3222,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C21" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E21" t="s">
         <v>214</v>
@@ -3222,10 +3234,10 @@
         <v>214</v>
       </c>
       <c r="G21" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="K21" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -3233,22 +3245,22 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C22" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E22" t="s">
         <v>164</v>
       </c>
       <c r="F22" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="G22" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -3256,19 +3268,19 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C23" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="G23" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -3277,19 +3289,19 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C24" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E24" t="s">
         <v>164</v>
       </c>
       <c r="F24" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="G24" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -3298,19 +3310,19 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C25" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E25" t="s">
         <v>164</v>
       </c>
       <c r="F25" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -3318,19 +3330,19 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C26" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E26" t="s">
         <v>164</v>
       </c>
       <c r="F26" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -3338,19 +3350,19 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C27" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E27" t="s">
         <v>164</v>
       </c>
       <c r="F27" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -3358,22 +3370,22 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C28" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E28" t="s">
         <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G28" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -3381,22 +3393,22 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C29" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E29" t="s">
         <v>164</v>
       </c>
       <c r="F29" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G29" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -3404,19 +3416,19 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C30" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E30" t="s">
         <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3424,19 +3436,19 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C31" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E31" t="s">
         <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -5212,7 +5224,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C100" t="s">
         <v>434</v>
@@ -5238,7 +5250,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C101" t="s">
         <v>451</v>
@@ -5264,7 +5276,7 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C102" t="s">
         <v>453</v>
@@ -5290,7 +5302,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C103" t="s">
         <v>455</v>
@@ -5316,7 +5328,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C104" t="s">
         <v>457</v>
@@ -5342,7 +5354,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C105" t="s">
         <v>459</v>
@@ -5368,7 +5380,7 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C106" t="s">
         <v>461</v>
@@ -5394,7 +5406,7 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C107" t="s">
         <v>437</v>
@@ -5420,7 +5432,7 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C108" t="s">
         <v>439</v>
@@ -5446,7 +5458,7 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C109" t="s">
         <v>441</v>
@@ -5472,7 +5484,7 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C110" t="s">
         <v>443</v>
@@ -5498,7 +5510,7 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C111" t="s">
         <v>445</v>
@@ -5524,7 +5536,7 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C112" t="s">
         <v>447</v>
@@ -5550,7 +5562,7 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C113" t="s">
         <v>449</v>
@@ -5576,7 +5588,7 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C114" t="s">
         <v>216</v>
@@ -5602,7 +5614,7 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C115" t="s">
         <v>224</v>
@@ -5628,7 +5640,7 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C116" t="s">
         <v>240</v>
@@ -5654,7 +5666,7 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C117" t="s">
         <v>226</v>
@@ -5680,7 +5692,7 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C118" t="s">
         <v>228</v>
@@ -5706,7 +5718,7 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C119" t="s">
         <v>230</v>
@@ -5732,7 +5744,7 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C120" t="s">
         <v>232</v>
@@ -5758,7 +5770,7 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C121" t="s">
         <v>234</v>
@@ -5784,7 +5796,7 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C122" t="s">
         <v>236</v>
@@ -5810,7 +5822,7 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C123" t="s">
         <v>238</v>
@@ -5836,7 +5848,7 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C124" t="s">
         <v>463</v>
@@ -5862,7 +5874,7 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C125" t="s">
         <v>479</v>
@@ -5888,7 +5900,7 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C126" t="s">
         <v>481</v>
@@ -5914,7 +5926,7 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C127" t="s">
         <v>483</v>
@@ -5940,7 +5952,7 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C128" t="s">
         <v>485</v>
@@ -5966,7 +5978,7 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C129" t="s">
         <v>465</v>
@@ -5992,7 +6004,7 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C130" t="s">
         <v>467</v>
@@ -6018,7 +6030,7 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C131" t="s">
         <v>469</v>
@@ -6044,7 +6056,7 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C132" t="s">
         <v>471</v>
@@ -6070,7 +6082,7 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C133" t="s">
         <v>473</v>
@@ -6096,7 +6108,7 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C134" t="s">
         <v>475</v>
@@ -6122,7 +6134,7 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C135" t="s">
         <v>477</v>
@@ -6148,7 +6160,7 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C136" t="s">
         <v>221</v>
@@ -6177,7 +6189,7 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C137" t="s">
         <v>245</v>
@@ -6203,7 +6215,7 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C138" t="s">
         <v>255</v>
@@ -6229,7 +6241,7 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C139" t="s">
         <v>281</v>
@@ -7087,7 +7099,7 @@
         <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C172" t="s">
         <v>343</v>
@@ -7102,7 +7114,7 @@
         <v>196</v>
       </c>
       <c r="I172" t="s">
-        <v>243</v>
+        <v>751</v>
       </c>
       <c r="K172" t="s">
         <v>17</v>
@@ -7919,7 +7931,7 @@
         <v>11</v>
       </c>
       <c r="B204" t="s">
-        <v>556</v>
+        <v>757</v>
       </c>
       <c r="C204" t="s">
         <v>385</v>
@@ -7934,7 +7946,7 @@
         <v>196</v>
       </c>
       <c r="I204" t="s">
-        <v>243</v>
+        <v>753</v>
       </c>
       <c r="K204" t="s">
         <v>17</v>
@@ -7945,7 +7957,7 @@
         <v>11</v>
       </c>
       <c r="B205" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C205" t="s">
         <v>387</v>
@@ -7971,7 +7983,7 @@
         <v>11</v>
       </c>
       <c r="B206" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C206" t="s">
         <v>389</v>
@@ -7997,7 +8009,7 @@
         <v>11</v>
       </c>
       <c r="B207" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C207" t="s">
         <v>391</v>
@@ -8023,7 +8035,7 @@
         <v>11</v>
       </c>
       <c r="B208" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C208" t="s">
         <v>393</v>
@@ -8049,7 +8061,7 @@
         <v>11</v>
       </c>
       <c r="B209" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C209" t="s">
         <v>395</v>
@@ -8075,7 +8087,7 @@
         <v>11</v>
       </c>
       <c r="B210" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C210" t="s">
         <v>397</v>
@@ -8101,7 +8113,7 @@
         <v>11</v>
       </c>
       <c r="B211" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C211" t="s">
         <v>399</v>
@@ -8127,7 +8139,7 @@
         <v>11</v>
       </c>
       <c r="B212" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C212" t="s">
         <v>401</v>
@@ -8153,7 +8165,7 @@
         <v>11</v>
       </c>
       <c r="B213" t="s">
-        <v>565</v>
+        <v>755</v>
       </c>
       <c r="C213" t="s">
         <v>403</v>
@@ -8168,7 +8180,7 @@
         <v>196</v>
       </c>
       <c r="I213" t="s">
-        <v>243</v>
+        <v>753</v>
       </c>
       <c r="K213" t="s">
         <v>17</v>
@@ -8179,7 +8191,7 @@
         <v>11</v>
       </c>
       <c r="B214" t="s">
-        <v>566</v>
+        <v>752</v>
       </c>
       <c r="C214" t="s">
         <v>405</v>
@@ -8194,7 +8206,7 @@
         <v>196</v>
       </c>
       <c r="I214" t="s">
-        <v>243</v>
+        <v>750</v>
       </c>
       <c r="K214" t="s">
         <v>17</v>
@@ -8205,7 +8217,7 @@
         <v>11</v>
       </c>
       <c r="B215" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C215" t="s">
         <v>407</v>
@@ -8257,7 +8269,7 @@
         <v>11</v>
       </c>
       <c r="B217" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C217" t="s">
         <v>409</v>
@@ -8283,7 +8295,7 @@
         <v>11</v>
       </c>
       <c r="B218" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C218" t="s">
         <v>411</v>
@@ -8309,7 +8321,7 @@
         <v>11</v>
       </c>
       <c r="B219" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C219" t="s">
         <v>413</v>
@@ -8335,7 +8347,7 @@
         <v>11</v>
       </c>
       <c r="B220" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C220" t="s">
         <v>415</v>
@@ -8387,7 +8399,7 @@
         <v>11</v>
       </c>
       <c r="B222" t="s">
-        <v>572</v>
+        <v>756</v>
       </c>
       <c r="C222" t="s">
         <v>417</v>
@@ -8402,7 +8414,7 @@
         <v>196</v>
       </c>
       <c r="I222" t="s">
-        <v>243</v>
+        <v>749</v>
       </c>
       <c r="K222" t="s">
         <v>17</v>
@@ -8413,7 +8425,7 @@
         <v>11</v>
       </c>
       <c r="B223" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C223" t="s">
         <v>419</v>
@@ -8439,7 +8451,7 @@
         <v>11</v>
       </c>
       <c r="B224" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C224" t="s">
         <v>427</v>
@@ -8465,7 +8477,7 @@
         <v>11</v>
       </c>
       <c r="B225" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C225" t="s">
         <v>429</v>
@@ -8491,7 +8503,7 @@
         <v>11</v>
       </c>
       <c r="B226" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C226" t="s">
         <v>431</v>
@@ -8647,28 +8659,28 @@
         <v>11</v>
       </c>
       <c r="B232" t="s">
+        <v>720</v>
+      </c>
+      <c r="C232" t="s">
+        <v>721</v>
+      </c>
+      <c r="E232" t="s">
+        <v>196</v>
+      </c>
+      <c r="F232" t="s">
+        <v>722</v>
+      </c>
+      <c r="G232" t="s">
+        <v>723</v>
+      </c>
+      <c r="H232" t="s">
+        <v>720</v>
+      </c>
+      <c r="I232" t="s">
         <v>724</v>
       </c>
-      <c r="C232" t="s">
+      <c r="K232" t="s">
         <v>725</v>
-      </c>
-      <c r="E232" t="s">
-        <v>196</v>
-      </c>
-      <c r="F232" t="s">
-        <v>726</v>
-      </c>
-      <c r="G232" t="s">
-        <v>727</v>
-      </c>
-      <c r="H232" t="s">
-        <v>724</v>
-      </c>
-      <c r="I232" t="s">
-        <v>728</v>
-      </c>
-      <c r="K232" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.2">
@@ -8676,28 +8688,28 @@
         <v>11</v>
       </c>
       <c r="B233" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C233" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E233" t="s">
         <v>196</v>
       </c>
       <c r="F233" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G233" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H233" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="I233" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K233" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.2">
@@ -8705,28 +8717,28 @@
         <v>11</v>
       </c>
       <c r="B234" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C234" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E234" t="s">
         <v>196</v>
       </c>
       <c r="F234" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G234" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H234" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="I234" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K234" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.2">
@@ -8734,28 +8746,28 @@
         <v>11</v>
       </c>
       <c r="B235" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C235" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E235" t="s">
         <v>196</v>
       </c>
       <c r="F235" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G235" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H235" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="I235" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K235" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.2">
@@ -8763,28 +8775,28 @@
         <v>11</v>
       </c>
       <c r="B236" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C236" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="E236" t="s">
         <v>196</v>
       </c>
       <c r="F236" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G236" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H236" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="I236" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K236" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.2">
@@ -8792,28 +8804,28 @@
         <v>11</v>
       </c>
       <c r="B237" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C237" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="E237" t="s">
         <v>196</v>
       </c>
       <c r="F237" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G237" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H237" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="I237" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K237" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.2">
@@ -8821,28 +8833,28 @@
         <v>11</v>
       </c>
       <c r="B238" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C238" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E238" t="s">
         <v>196</v>
       </c>
       <c r="F238" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G238" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H238" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="I238" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K238" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
@@ -8850,28 +8862,28 @@
         <v>11</v>
       </c>
       <c r="B239" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C239" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E239" t="s">
         <v>196</v>
       </c>
       <c r="F239" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G239" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H239" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="I239" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="K239" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="448" spans="10:10" x14ac:dyDescent="0.2">
